--- a/A_Main_Code/Outcome/Results_oneside.xlsx
+++ b/A_Main_Code/Outcome/Results_oneside.xlsx
@@ -56,9 +56,9 @@
   <dimension ref="A1:C197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="true"/>
+    <col min="1" max="1" width="16.08984375" customWidth="true"/>
     <col min="2" max="2" width="15.453125" customWidth="true"/>
-    <col min="3" max="3" width="16.08984375" customWidth="true"/>
+    <col min="3" max="3" width="15.08984375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -78,1687 +78,1801 @@
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.0029280729995517368</v>
+        <v>0.012204321031621647</v>
       </c>
       <c r="B4" s="0">
-        <v>0.038156254919104883</v>
+        <v>0.061532240404159423</v>
       </c>
       <c r="C4" s="0">
-        <v>0.065267870994766386</v>
+        <v>0.14340819531294563</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.00023678590981233635</v>
+        <v>0.0064614488550446929</v>
       </c>
       <c r="B5" s="0">
-        <v>0.04013391221944735</v>
+        <v>0.051561156309802125</v>
       </c>
       <c r="C5" s="0">
-        <v>0.060581275577510738</v>
+        <v>0.11727872627754089</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>-1.0650387136029033e-05</v>
+        <v>0.0041307925948767046</v>
       </c>
       <c r="B6" s="0">
-        <v>0.03967324659336946</v>
+        <v>0.048508316092340964</v>
       </c>
       <c r="C6" s="0">
-        <v>0.074992645578933662</v>
+        <v>0.13616227587620927</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>0.008929007322946084</v>
+        <v>0.014339006638751147</v>
       </c>
       <c r="B7" s="0">
-        <v>0.043944216243239347</v>
+        <v>0.05668945187718348</v>
       </c>
       <c r="C7" s="0">
-        <v>0.087807136528704921</v>
+        <v>0.15147235346032009</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.017652586679752821</v>
+        <v>0.025252026701407585</v>
       </c>
       <c r="B8" s="0">
-        <v>0.046980031706059383</v>
+        <v>0.062830739112879355</v>
       </c>
       <c r="C8" s="0">
-        <v>0.099254294568252771</v>
+        <v>0.15731781166301539</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.026348678563478528</v>
+        <v>0.031524634704907968</v>
       </c>
       <c r="B9" s="0">
-        <v>0.055338093997246346</v>
+        <v>0.063119089705911666</v>
       </c>
       <c r="C9" s="0">
-        <v>0.11149395617112243</v>
+        <v>0.15494965268153879</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>0.038538309977051835</v>
+        <v>0.042636404024452984</v>
       </c>
       <c r="B10" s="0">
-        <v>0.072819938787714839</v>
+        <v>0.079702720283749848</v>
       </c>
       <c r="C10" s="0">
-        <v>0.115222254426531</v>
+        <v>0.16207439360991718</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>0.042056910126312463</v>
+        <v>0.047403382930893266</v>
       </c>
       <c r="B11" s="0">
-        <v>0.079217183901551191</v>
+        <v>0.088463172886981412</v>
       </c>
       <c r="C11" s="0">
-        <v>0.10927289138210909</v>
+        <v>0.15970783113696166</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>0.047965205330558043</v>
+        <v>0.053716445377336441</v>
       </c>
       <c r="B12" s="0">
-        <v>0.092397573618558729</v>
+        <v>0.10236827623084938</v>
       </c>
       <c r="C12" s="0">
-        <v>0.12666715991197783</v>
+        <v>0.1700865173638787</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>0.057237308068168243</v>
+        <v>0.061437464743827316</v>
       </c>
       <c r="B13" s="0">
-        <v>0.1104874509926357</v>
+        <v>0.11613333891047245</v>
       </c>
       <c r="C13" s="0">
-        <v>0.14568014512030097</v>
+        <v>0.18214080340841143</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>0.063973545627852943</v>
+        <v>0.06693010100229882</v>
       </c>
       <c r="B14" s="0">
-        <v>0.12565057319103753</v>
+        <v>0.13072957555943593</v>
       </c>
       <c r="C14" s="0">
-        <v>0.14014491106637808</v>
+        <v>0.17126027205067665</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>0.072483765826829097</v>
+        <v>0.077351565500005035</v>
       </c>
       <c r="B15" s="0">
-        <v>0.13172010002583484</v>
+        <v>0.13844563932369233</v>
       </c>
       <c r="C15" s="0">
-        <v>0.12823216693333359</v>
+        <v>0.16933409172280964</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>0.074204718344392268</v>
+        <v>0.07843840470481532</v>
       </c>
       <c r="B16" s="0">
-        <v>0.12627832497940791</v>
+        <v>0.13255589264847459</v>
       </c>
       <c r="C16" s="0">
-        <v>0.12374953413157951</v>
+        <v>0.15544919217120909</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>0.071220619781046851</v>
+        <v>0.073945417890299237</v>
       </c>
       <c r="B17" s="0">
-        <v>0.1219835364681132</v>
+        <v>0.1256925555069465</v>
       </c>
       <c r="C17" s="0">
-        <v>0.12404798792928409</v>
+        <v>0.14936422929086701</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0.067738280067303688</v>
+        <v>0.070403844399033202</v>
       </c>
       <c r="B18" s="0">
-        <v>0.12106681251963963</v>
+        <v>0.12490717321595116</v>
       </c>
       <c r="C18" s="0">
-        <v>0.12815490898656129</v>
+        <v>0.1522838110791204</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0.061262633181699389</v>
+        <v>0.06555458316859257</v>
       </c>
       <c r="B19" s="0">
-        <v>0.11936074620470538</v>
+        <v>0.12401856874518459</v>
       </c>
       <c r="C19" s="0">
-        <v>0.10928090809014274</v>
+        <v>0.14337363735980757</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0.057349185669244226</v>
+        <v>0.060369429149809598</v>
       </c>
       <c r="B20" s="0">
-        <v>0.11978682481751642</v>
+        <v>0.12322363370055389</v>
       </c>
       <c r="C20" s="0">
-        <v>0.10303831135637825</v>
+        <v>0.12483643479102577</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0.052841147957264814</v>
+        <v>0.053950942448823348</v>
       </c>
       <c r="B21" s="0">
-        <v>0.1158996707508726</v>
+        <v>0.11713210221172909</v>
       </c>
       <c r="C21" s="0">
-        <v>0.088147247094890385</v>
+        <v>0.10490018197069489</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>0.046611838668091536</v>
+        <v>0.048766046832260962</v>
       </c>
       <c r="B22" s="0">
-        <v>0.10691536236913918</v>
+        <v>0.1111256354069704</v>
       </c>
       <c r="C22" s="0">
-        <v>0.074635818016832833</v>
+        <v>0.090869356150177313</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.044122017657623434</v>
+        <v>0.047710722051722748</v>
       </c>
       <c r="B23" s="0">
-        <v>0.10347062696484</v>
+        <v>0.10732996962338161</v>
       </c>
       <c r="C23" s="0">
-        <v>0.081412666911913359</v>
+        <v>0.11155292370543893</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0.042290907929565136</v>
+        <v>0.044198808579897331</v>
       </c>
       <c r="B24" s="0">
-        <v>0.10351350581724247</v>
+        <v>0.10621722861538499</v>
       </c>
       <c r="C24" s="0">
-        <v>0.060903381365241198</v>
+        <v>0.075467794604078764</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.038985115670492912</v>
+        <v>0.040453158069017676</v>
       </c>
       <c r="B25" s="0">
-        <v>0.099142175930721832</v>
+        <v>0.10154537781202438</v>
       </c>
       <c r="C25" s="0">
-        <v>0.035883397743970334</v>
+        <v>0.048589881850101165</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0.036017447915292843</v>
+        <v>0.036960932330676391</v>
       </c>
       <c r="B26" s="0">
-        <v>0.091099182253864069</v>
+        <v>0.092868547185047681</v>
       </c>
       <c r="C26" s="0">
-        <v>0.03325067810343045</v>
+        <v>0.041911825148212387</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.031516995252818092</v>
+        <v>0.03425289816104992</v>
       </c>
       <c r="B27" s="0">
-        <v>0.082101800251501655</v>
+        <v>0.084416940259713691</v>
       </c>
       <c r="C27" s="0">
-        <v>0.036919998017956479</v>
+        <v>0.061788288824081737</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0.026328804211022655</v>
+        <v>0.027490942724123318</v>
       </c>
       <c r="B28" s="0">
-        <v>0.073125971585081787</v>
+        <v>0.074897862536394105</v>
       </c>
       <c r="C28" s="0">
-        <v>0.029894417208235349</v>
+        <v>0.038152507868289227</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>0.022698393375081387</v>
+        <v>0.023444078037466214</v>
       </c>
       <c r="B29" s="0">
-        <v>0.067774628308287607</v>
+        <v>0.06957662691027329</v>
       </c>
       <c r="C29" s="0">
-        <v>0.044336027405193386</v>
+        <v>0.050795582597490688</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.02039942936573462</v>
+        <v>0.021468529665447909</v>
       </c>
       <c r="B30" s="0">
-        <v>0.067573148032444991</v>
+        <v>0.069223529746435586</v>
       </c>
       <c r="C30" s="0">
-        <v>0.01576825402076848</v>
+        <v>0.023442860299406412</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>0.016968336706418567</v>
+        <v>0.0191633607278805</v>
       </c>
       <c r="B31" s="0">
-        <v>0.059937184333122805</v>
+        <v>0.061444357234566205</v>
       </c>
       <c r="C31" s="0">
-        <v>0.023560756793481727</v>
+        <v>0.041251820833335839</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>0.0093731186864490501</v>
+        <v>0.010139540678881322</v>
       </c>
       <c r="B32" s="0">
-        <v>0.049293403784326742</v>
+        <v>0.049846445221787924</v>
       </c>
       <c r="C32" s="0">
-        <v>0.0042637542197823796</v>
+        <v>0.0077915379360009897</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>0.0026570147625244603</v>
+        <v>0.0025615621463052586</v>
       </c>
       <c r="B33" s="0">
-        <v>0.039541406728243661</v>
+        <v>0.039828075563266056</v>
       </c>
       <c r="C33" s="0">
-        <v>-0.019391579105395039</v>
+        <v>-0.014548539057708657</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>-0.0011574802591247492</v>
+        <v>-0.0003960663056716213</v>
       </c>
       <c r="B34" s="0">
-        <v>0.029578810860462285</v>
+        <v>0.03212780652764953</v>
       </c>
       <c r="C34" s="0">
-        <v>-0.021648402030715864</v>
+        <v>-0.018226799559068786</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>-0.0030864926082119948</v>
+        <v>-0.0014236194561525165</v>
       </c>
       <c r="B35" s="0">
-        <v>0.019559697051609905</v>
+        <v>0.021311967267696311</v>
       </c>
       <c r="C35" s="0">
-        <v>-0.02697872129650207</v>
+        <v>-0.014950478547336592</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>-0.0049356251150591696</v>
+        <v>-0.0044990531187321069</v>
       </c>
       <c r="B36" s="0">
-        <v>0.0071409355169835056</v>
+        <v>0.0079214522103200659</v>
       </c>
       <c r="C36" s="0">
-        <v>-0.02125379627327734</v>
+        <v>-0.019739921611653249</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>-0.0063862845825735952</v>
+        <v>-0.0061633418994864854</v>
       </c>
       <c r="B37" s="0">
-        <v>-0.005207562236789082</v>
+        <v>-0.0039224203908495119</v>
       </c>
       <c r="C37" s="0">
-        <v>-0.0077187848639983167</v>
+        <v>-0.0056642567351132544</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>-0.010124037001319424</v>
+        <v>-0.0095734767261155193</v>
       </c>
       <c r="B38" s="0">
-        <v>-0.016774281652696642</v>
+        <v>-0.015612620062148388</v>
       </c>
       <c r="C38" s="0">
-        <v>-0.012437959304642032</v>
+        <v>-0.0078528722879700405</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>-0.016068859800446946</v>
+        <v>-0.015313266362598624</v>
       </c>
       <c r="B39" s="0">
-        <v>-0.024969530040059841</v>
+        <v>-0.024192295526522793</v>
       </c>
       <c r="C39" s="0">
-        <v>-0.040611957731894216</v>
+        <v>-0.037049319705542053</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>-0.017208125436573317</v>
+        <v>-0.016985020490801556</v>
       </c>
       <c r="B40" s="0">
-        <v>-0.025100822732747691</v>
+        <v>-0.024655736015593264</v>
       </c>
       <c r="C40" s="0">
-        <v>-0.031143197356270528</v>
+        <v>-0.031753233876130556</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>-0.015330484344061271</v>
+        <v>-0.015063252403942819</v>
       </c>
       <c r="B41" s="0">
-        <v>-0.020840002204257121</v>
+        <v>-0.019677414683418278</v>
       </c>
       <c r="C41" s="0">
-        <v>-0.0048792877682935932</v>
+        <v>-0.0028474132103981521</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>-0.017341164839694896</v>
+        <v>-0.017130382060467443</v>
       </c>
       <c r="B42" s="0">
-        <v>-0.020063442948867461</v>
+        <v>-0.019168830857003424</v>
       </c>
       <c r="C42" s="0">
-        <v>-0.021013847257095038</v>
+        <v>-0.020821425658979521</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>-0.01139384014429796</v>
+        <v>-0.010767235268531029</v>
       </c>
       <c r="B43" s="0">
-        <v>-0.011014973021162904</v>
+        <v>-0.010493698224798753</v>
       </c>
       <c r="C43" s="0">
-        <v>-0.0047397580898035797</v>
+        <v>-0.0052479029242143496</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>-0.0052891342489358928</v>
+        <v>-0.0050098627494257631</v>
       </c>
       <c r="B44" s="0">
-        <v>-0.0078079915612601809</v>
+        <v>-0.0081654991703596601</v>
       </c>
       <c r="C44" s="0">
-        <v>0.016802114887863265</v>
+        <v>0.015850288943729914</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>-0.0021302744884398855</v>
+        <v>-0.0024820193554733177</v>
       </c>
       <c r="B45" s="0">
-        <v>-0.0061829870378948817</v>
+        <v>-0.0063463611201000254</v>
       </c>
       <c r="C45" s="0">
-        <v>0.0078105807623941124</v>
+        <v>0.0083375244410371502</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>0.001834448965498469</v>
+        <v>0.0018275250691441771</v>
       </c>
       <c r="B46" s="0">
-        <v>-0.0038168642490853844</v>
+        <v>-0.0020028940178103468</v>
       </c>
       <c r="C46" s="0">
-        <v>0.020304390399130064</v>
+        <v>0.018728438776793123</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>0.0058051942200776693</v>
+        <v>0.0061463643769913822</v>
       </c>
       <c r="B47" s="0">
-        <v>0.00011778727665965314</v>
+        <v>0.0011558758981244752</v>
       </c>
       <c r="C47" s="0">
-        <v>0.038344311187920962</v>
+        <v>0.034854522710070432</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>0.0061816002670791138</v>
+        <v>0.006287150801915253</v>
       </c>
       <c r="B48" s="0">
-        <v>0.0027630272505230328</v>
+        <v>0.002882085340925147</v>
       </c>
       <c r="C48" s="0">
-        <v>0.036013000447212111</v>
+        <v>0.034333584416584233</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>0.0030181296702880807</v>
+        <v>0.0029881677485263979</v>
       </c>
       <c r="B49" s="0">
-        <v>0.0025166345943580504</v>
+        <v>0.0031894709773303913</v>
       </c>
       <c r="C49" s="0">
-        <v>0.012609645898922361</v>
+        <v>0.011333632645528427</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>0.0010727659062663136</v>
+        <v>0.0010440495998898008</v>
       </c>
       <c r="B50" s="0">
-        <v>0.0040247532810255794</v>
+        <v>0.0046970359289611342</v>
       </c>
       <c r="C50" s="0">
-        <v>0.017788566131712622</v>
+        <v>0.016384566074012809</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>-0.0020593793289890522</v>
+        <v>-0.0023409406810089677</v>
       </c>
       <c r="B51" s="0">
-        <v>0.0015908525713974704</v>
+        <v>0.0017819170053649238</v>
       </c>
       <c r="C51" s="0">
-        <v>0.0090391131302267197</v>
+        <v>0.0019656840728054332</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>-0.0044673068364752509</v>
+        <v>-0.0044729002759590838</v>
       </c>
       <c r="B52" s="0">
-        <v>-0.005104248293572527</v>
+        <v>-0.0051102808757531679</v>
       </c>
       <c r="C52" s="0">
-        <v>0.010267253485493609</v>
+        <v>0.0073613791260802924</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>-0.0056903445679629258</v>
+        <v>-0.0054575900088344705</v>
       </c>
       <c r="B53" s="0">
-        <v>-0.011769243487389634</v>
+        <v>-0.011041884926667868</v>
       </c>
       <c r="C53" s="0">
-        <v>0.027358200362735993</v>
+        <v>0.026601083605979424</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>-0.0088529298054824124</v>
+        <v>-0.009364717109005976</v>
       </c>
       <c r="B54" s="0">
-        <v>-0.018159030913769678</v>
+        <v>-0.018046132794693984</v>
       </c>
       <c r="C54" s="0">
-        <v>-0.0016703752008314903</v>
+        <v>-0.0072920832298700366</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>-0.010006155855941008</v>
+        <v>-0.010442112510817801</v>
       </c>
       <c r="B55" s="0">
-        <v>-0.022576088110706802</v>
+        <v>-0.022485652737693047</v>
       </c>
       <c r="C55" s="0">
-        <v>-0.00062856035737921066</v>
+        <v>-0.0072175997066277918</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>-0.012369014590182359</v>
+        <v>-0.012432834946406309</v>
       </c>
       <c r="B56" s="0">
-        <v>-0.025836208621432277</v>
+        <v>-0.025815010079030296</v>
       </c>
       <c r="C56" s="0">
-        <v>-0.0031757839404693549</v>
+        <v>-0.0068386905657972438</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>-0.015686057737343783</v>
+        <v>-0.015148372493724358</v>
       </c>
       <c r="B57" s="0">
-        <v>-0.029287319901333507</v>
+        <v>-0.028292825189734323</v>
       </c>
       <c r="C57" s="0">
-        <v>-0.021251182643970749</v>
+        <v>-0.021857010334923356</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>-0.019614100538901363</v>
+        <v>-0.02049872870983634</v>
       </c>
       <c r="B58" s="0">
-        <v>-0.035788691560891796</v>
+        <v>-0.036224305281866362</v>
       </c>
       <c r="C58" s="0">
-        <v>-0.039180616464956956</v>
+        <v>-0.045393664796075775</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>-0.026618892142150997</v>
+        <v>-0.027385014343085913</v>
       </c>
       <c r="B59" s="0">
-        <v>-0.049181714365807067</v>
+        <v>-0.049371033957755203</v>
       </c>
       <c r="C59" s="0">
-        <v>-0.062845740763234043</v>
+        <v>-0.070693819257819035</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>-0.028959330394221789</v>
+        <v>-0.029068928856814152</v>
       </c>
       <c r="B60" s="0">
-        <v>-0.054919873422846148</v>
+        <v>-0.054716421553072277</v>
       </c>
       <c r="C60" s="0">
-        <v>-0.065278271650432818</v>
+        <v>-0.070895207479158409</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>-0.028778484561632907</v>
+        <v>-0.028495782574825296</v>
       </c>
       <c r="B61" s="0">
-        <v>-0.057804367262837088</v>
+        <v>-0.05718023418214891</v>
       </c>
       <c r="C61" s="0">
-        <v>-0.072050331079496571</v>
+        <v>-0.076690488433347498</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>-0.028886413620783594</v>
+        <v>-0.02929613151792787</v>
       </c>
       <c r="B62" s="0">
-        <v>-0.059538352265597477</v>
+        <v>-0.059932311216138338</v>
       </c>
       <c r="C62" s="0">
-        <v>-0.062715140989252557</v>
+        <v>-0.064465151980405103</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>-0.032079073663390252</v>
+        <v>-0.033096528029871147</v>
       </c>
       <c r="B63" s="0">
-        <v>-0.061836133903278689</v>
+        <v>-0.06247248981439852</v>
       </c>
       <c r="C63" s="0">
-        <v>-0.070850032823925879</v>
+        <v>-0.080367872124507841</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>-0.035676965921658615</v>
+        <v>-0.035683021924161097</v>
       </c>
       <c r="B64" s="0">
-        <v>-0.063740194113243484</v>
+        <v>-0.06393268149330128</v>
       </c>
       <c r="C64" s="0">
-        <v>-0.094097379615482604</v>
+        <v>-0.10062368358918634</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>-0.036830734537496038</v>
+        <v>-0.036956018461420867</v>
       </c>
       <c r="B65" s="0">
-        <v>-0.064574991363301082</v>
+        <v>-0.065088188813022751</v>
       </c>
       <c r="C65" s="0">
-        <v>-0.088882307975006819</v>
+        <v>-0.093699839369341412</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>-0.034806485740205242</v>
+        <v>-0.035374409839238195</v>
       </c>
       <c r="B66" s="0">
-        <v>-0.064982372428979668</v>
+        <v>-0.064756380851527948</v>
       </c>
       <c r="C66" s="0">
-        <v>-0.089059486759372017</v>
+        <v>-0.092373389811069545</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>-0.028790871565584637</v>
+        <v>-0.030018293712185156</v>
       </c>
       <c r="B67" s="0">
-        <v>-0.064722371691496305</v>
+        <v>-0.06493205149439675</v>
       </c>
       <c r="C67" s="0">
-        <v>-0.10492940691086955</v>
+        <v>-0.11367560098631933</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>-0.023744280306654882</v>
+        <v>-0.023706450157305978</v>
       </c>
       <c r="B68" s="0">
-        <v>-0.068108505600720029</v>
+        <v>-0.067324398833399593</v>
       </c>
       <c r="C68" s="0">
-        <v>-0.10996779145020713</v>
+        <v>-0.11585861181094079</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="0"/>
-      <c r="B69" s="0"/>
-      <c r="C69" s="0"/>
+      <c r="A69" s="0">
+        <v>-0.018962915586429856</v>
+      </c>
+      <c r="B69" s="0">
+        <v>-0.070705206390120692</v>
+      </c>
+      <c r="C69" s="0">
+        <v>-0.11753341187970814</v>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="0"/>
-      <c r="B70" s="0"/>
-      <c r="C70" s="0"/>
+      <c r="A70" s="0">
+        <v>-0.017865329186713588</v>
+      </c>
+      <c r="B70" s="0">
+        <v>-0.072496518641967822</v>
+      </c>
+      <c r="C70" s="0">
+        <v>-0.11189626840514649</v>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="0"/>
-      <c r="B71" s="0"/>
-      <c r="C71" s="0"/>
+      <c r="A71" s="0">
+        <v>-0.018797369042604609</v>
+      </c>
+      <c r="B71" s="0">
+        <v>-0.070236334245516854</v>
+      </c>
+      <c r="C71" s="0">
+        <v>-0.11139210256748164</v>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="0"/>
-      <c r="B72" s="0"/>
-      <c r="C72" s="0"/>
+      <c r="A72" s="0">
+        <v>-0.018424418309384984</v>
+      </c>
+      <c r="B72" s="0">
+        <v>-0.065487231014382294</v>
+      </c>
+      <c r="C72" s="0">
+        <v>-0.10897562519101017</v>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="0"/>
-      <c r="B73" s="0"/>
-      <c r="C73" s="0"/>
+      <c r="A73" s="0">
+        <v>-0.016217978765700445</v>
+      </c>
+      <c r="B73" s="0">
+        <v>-0.063223624686272434</v>
+      </c>
+      <c r="C73" s="0">
+        <v>-0.10106555759177722</v>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="0"/>
-      <c r="B74" s="0"/>
-      <c r="C74" s="0"/>
+      <c r="A74" s="0">
+        <v>-0.018115564340822145</v>
+      </c>
+      <c r="B74" s="0">
+        <v>-0.06793057174075226</v>
+      </c>
+      <c r="C74" s="0">
+        <v>-0.10415230116856539</v>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="0"/>
-      <c r="B75" s="0"/>
-      <c r="C75" s="0"/>
+      <c r="A75" s="0">
+        <v>-0.015730941473213279</v>
+      </c>
+      <c r="B75" s="0">
+        <v>-0.064844732569211236</v>
+      </c>
+      <c r="C75" s="0">
+        <v>-0.11034688804436478</v>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="0"/>
-      <c r="B76" s="0"/>
-      <c r="C76" s="0"/>
+      <c r="A76" s="0">
+        <v>-0.010412209244336147</v>
+      </c>
+      <c r="B76" s="0">
+        <v>-0.059668417444126938</v>
+      </c>
+      <c r="C76" s="0">
+        <v>-0.10379954802951866</v>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="0"/>
-      <c r="B77" s="0"/>
-      <c r="C77" s="0"/>
+      <c r="A77" s="0">
+        <v>-0.012028817630107647</v>
+      </c>
+      <c r="B77" s="0">
+        <v>-0.05786332696320598</v>
+      </c>
+      <c r="C77" s="0">
+        <v>-0.10222203717426538</v>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="0"/>
-      <c r="B78" s="0"/>
-      <c r="C78" s="0"/>
+      <c r="A78" s="0">
+        <v>-0.025820297746935811</v>
+      </c>
+      <c r="B78" s="0">
+        <v>-0.058918353972009029</v>
+      </c>
+      <c r="C78" s="0">
+        <v>-0.087269074106986783</v>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="0"/>
-      <c r="B79" s="0"/>
-      <c r="C79" s="0"/>
+      <c r="A79" s="0">
+        <v>-0.029056395625320808</v>
+      </c>
+      <c r="B79" s="0">
+        <v>-0.052301532333923872</v>
+      </c>
+      <c r="C79" s="0">
+        <v>-0.068091608501627432</v>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="0"/>
-      <c r="B80" s="0"/>
-      <c r="C80" s="0"/>
+      <c r="A80" s="0">
+        <v>-0.02375492977239194</v>
+      </c>
+      <c r="B80" s="0">
+        <v>-0.041914636321767854</v>
+      </c>
+      <c r="C80" s="0">
+        <v>-0.039311672475701401</v>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="0"/>
-      <c r="B81" s="0"/>
-      <c r="C81" s="0"/>
+      <c r="A81" s="0">
+        <v>-0.023723022384712612</v>
+      </c>
+      <c r="B81" s="0">
+        <v>-0.039541414554699644</v>
+      </c>
+      <c r="C81" s="0">
+        <v>-0.038190744656260843</v>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="0"/>
-      <c r="B82" s="0"/>
-      <c r="C82" s="0"/>
+      <c r="A82" s="0">
+        <v>-0.025570955856398021</v>
+      </c>
+      <c r="B82" s="0">
+        <v>-0.035671748708028181</v>
+      </c>
+      <c r="C82" s="0">
+        <v>-0.032315670404047835</v>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="0"/>
-      <c r="B83" s="0"/>
-      <c r="C83" s="0"/>
+      <c r="A83" s="0">
+        <v>-0.026162189675682221</v>
+      </c>
+      <c r="B83" s="0">
+        <v>-0.028929540902292564</v>
+      </c>
+      <c r="C83" s="0">
+        <v>-0.028949367382415301</v>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="0"/>
-      <c r="B84" s="0"/>
-      <c r="C84" s="0"/>
+      <c r="A84" s="0">
+        <v>-0.025161594002602206</v>
+      </c>
+      <c r="B84" s="0">
+        <v>-0.022410693367065186</v>
+      </c>
+      <c r="C84" s="0">
+        <v>-0.020327258197168345</v>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="0"/>
-      <c r="B85" s="0"/>
-      <c r="C85" s="0"/>
+      <c r="A85" s="0">
+        <v>-0.020053211401397989</v>
+      </c>
+      <c r="B85" s="0">
+        <v>-0.012678857926532965</v>
+      </c>
+      <c r="C85" s="0">
+        <v>-0.005547847049351364</v>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="0"/>
-      <c r="B86" s="0"/>
-      <c r="C86" s="0"/>
+      <c r="A86" s="0">
+        <v>-0.010841537936623916</v>
+      </c>
+      <c r="B86" s="0">
+        <v>-0.0024874751973388998</v>
+      </c>
+      <c r="C86" s="0">
+        <v>0.010196170359660913</v>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="0"/>
-      <c r="B87" s="0"/>
-      <c r="C87" s="0"/>
+      <c r="A87" s="0">
+        <v>-0.0019119766900489094</v>
+      </c>
+      <c r="B87" s="0">
+        <v>0.0037309250323454904</v>
+      </c>
+      <c r="C87" s="0">
+        <v>0.017524003858952863</v>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="0"/>
-      <c r="B88" s="0"/>
-      <c r="C88" s="0"/>
+      <c r="A88" s="0">
+        <v>0.0050997598812084072</v>
+      </c>
+      <c r="B88" s="0">
+        <v>0.008895546661262254</v>
+      </c>
+      <c r="C88" s="0">
+        <v>0.020915479094927636</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0.010548465992588915</v>
+        <v>0.010693441712333615</v>
       </c>
       <c r="B89" s="0">
-        <v>0.011439218161129128</v>
+        <v>0.011478162951740045</v>
       </c>
       <c r="C89" s="0">
-        <v>0.032952064544260813</v>
+        <v>0.027469329616462448</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.014495245803872552</v>
+        <v>0.013017261437094387</v>
       </c>
       <c r="B90" s="0">
-        <v>0.013096586157574128</v>
+        <v>0.01110784922080283</v>
       </c>
       <c r="C90" s="0">
-        <v>0.041956725312382044</v>
+        <v>0.037011193476213809</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.014385419485756706</v>
+        <v>0.013886700681681801</v>
       </c>
       <c r="B91" s="0">
-        <v>0.011268808819763051</v>
+        <v>0.011102318186439352</v>
       </c>
       <c r="C91" s="0">
-        <v>0.031756502563759705</v>
+        <v>0.02776438895793672</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0.012410772286764363</v>
+        <v>0.012400783755208948</v>
       </c>
       <c r="B92" s="0">
-        <v>0.0075328207059919281</v>
+        <v>0.007866185279784008</v>
       </c>
       <c r="C92" s="0">
-        <v>0.016765554641305368</v>
+        <v>0.010127340254316788</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>0.010097178135201021</v>
+        <v>0.009665631538448129</v>
       </c>
       <c r="B93" s="0">
-        <v>0.0015844956388884565</v>
+        <v>0.00097663659916256019</v>
       </c>
       <c r="C93" s="0">
-        <v>0.013492377736156188</v>
+        <v>0.0054362621121250322</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>0.0066337407449763765</v>
+        <v>0.0057819162903445</v>
       </c>
       <c r="B94" s="0">
-        <v>-0.0054312973282812475</v>
+        <v>-0.0068569498560921644</v>
       </c>
       <c r="C94" s="0">
-        <v>0.0018627926892496633</v>
+        <v>0.0015534264957910882</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0.0077904851524932834</v>
+        <v>0.007329999063387849</v>
       </c>
       <c r="B95" s="0">
-        <v>-0.006030819273738398</v>
+        <v>-0.0061491043382368108</v>
       </c>
       <c r="C95" s="0">
-        <v>0.016464755313884111</v>
+        <v>0.011783405309215724</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>0.0086133150272205625</v>
+        <v>0.008499163649755892</v>
       </c>
       <c r="B96" s="0">
-        <v>-0.0056231161200670102</v>
+        <v>-0.0053741012147210457</v>
       </c>
       <c r="C96" s="0">
-        <v>0.026781314947057638</v>
+        <v>0.019740371893554515</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0.010304094664588787</v>
+        <v>0.010016916744059266</v>
       </c>
       <c r="B97" s="0">
-        <v>-0.0021612399979002795</v>
+        <v>-0.0026382222662860609</v>
       </c>
       <c r="C97" s="0">
-        <v>0.034441713643661873</v>
+        <v>0.028709582294670979</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>0.013584578175303548</v>
+        <v>0.012432117436572292</v>
       </c>
       <c r="B98" s="0">
-        <v>0.0040127077510341653</v>
+        <v>0.0022851471298013879</v>
       </c>
       <c r="C98" s="0">
-        <v>0.041603390716840015</v>
+        <v>0.03820614182669628</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0.013013209657541536</v>
+        <v>0.012765766797392299</v>
       </c>
       <c r="B99" s="0">
-        <v>0.0034468879825744862</v>
+        <v>0.0034076182565808931</v>
       </c>
       <c r="C99" s="0">
-        <v>0.047967548695671915</v>
+        <v>0.045200085217194541</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>0.010716613186229764</v>
+        <v>0.010637381205123569</v>
       </c>
       <c r="B100" s="0">
-        <v>0.001989177624105604</v>
+        <v>0.0022389674386873726</v>
       </c>
       <c r="C100" s="0">
-        <v>0.052762964786740314</v>
+        <v>0.046930831170107053</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0">
-        <v>0.011673950188172534</v>
+        <v>0.011631518772461396</v>
       </c>
       <c r="B101" s="0">
-        <v>0.0047583808551665604</v>
+        <v>0.0046593676406591674</v>
       </c>
       <c r="C101" s="0">
-        <v>0.066669346426055834</v>
+        <v>0.063355733950921519</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0">
-        <v>0.014312666935240819</v>
+        <v>0.012891069367651109</v>
       </c>
       <c r="B102" s="0">
-        <v>0.012916000850890603</v>
+        <v>0.010968660195936598</v>
       </c>
       <c r="C102" s="0">
-        <v>0.084255227881838188</v>
+        <v>0.079751768659812816</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0">
-        <v>0.015450864869390762</v>
+        <v>0.015289360765310249</v>
       </c>
       <c r="B103" s="0">
-        <v>0.021036552688956725</v>
+        <v>0.020972666195946794</v>
       </c>
       <c r="C103" s="0">
-        <v>0.086415368475721413</v>
+        <v>0.083662532939411033</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0">
-        <v>0.016793325222237494</v>
+        <v>0.016687309217769435</v>
       </c>
       <c r="B104" s="0">
-        <v>0.029975726485693584</v>
+        <v>0.030191998663346029</v>
       </c>
       <c r="C104" s="0">
-        <v>0.083703465835227309</v>
+        <v>0.077445750575307226</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0">
-        <v>0.015539477649833721</v>
+        <v>0.015164287026140037</v>
       </c>
       <c r="B105" s="0">
-        <v>0.035757426896402308</v>
+        <v>0.035327590068792394</v>
       </c>
       <c r="C105" s="0">
-        <v>0.069419119547741853</v>
+        <v>0.064154010956471871</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0">
-        <v>0.015136398811753252</v>
+        <v>0.014390335593685272</v>
       </c>
       <c r="B106" s="0">
-        <v>0.042626521507635018</v>
+        <v>0.041283473898318608</v>
       </c>
       <c r="C106" s="0">
-        <v>0.060455831831184387</v>
+        <v>0.060416115377026555</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0">
-        <v>0.017659967290373994</v>
+        <v>0.017526400557028823</v>
       </c>
       <c r="B107" s="0">
-        <v>0.053662590980768581</v>
+        <v>0.05328291963757488</v>
       </c>
       <c r="C107" s="0">
-        <v>0.066640625362670194</v>
+        <v>0.063020733579209523</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0">
-        <v>0.023015095000711909</v>
+        <v>0.022989458527464274</v>
       </c>
       <c r="B108" s="0">
-        <v>0.067843131520741937</v>
+        <v>0.067461551175625994</v>
       </c>
       <c r="C108" s="0">
-        <v>0.083859327700315081</v>
+        <v>0.077175763904810582</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0">
-        <v>0.030914877929909816</v>
+        <v>0.030316461851039873</v>
       </c>
       <c r="B109" s="0">
-        <v>0.083363917841017418</v>
+        <v>0.082115539825908135</v>
       </c>
       <c r="C109" s="0">
-        <v>0.10695630489627021</v>
+        <v>0.1037804216553963</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0">
-        <v>0.038507480882498904</v>
+        <v>0.037602085108332371</v>
       </c>
       <c r="B110" s="0">
-        <v>0.096525497593184101</v>
+        <v>0.096142199696650527</v>
       </c>
       <c r="C110" s="0">
-        <v>0.12036269932208521</v>
+        <v>0.11925827784730374</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0">
-        <v>0.04892593930744555</v>
+        <v>0.048853221552284977</v>
       </c>
       <c r="B111" s="0">
-        <v>0.11314882630122125</v>
+        <v>0.11334467070444827</v>
       </c>
       <c r="C111" s="0">
-        <v>0.14905086533764433</v>
+        <v>0.14695121962492591</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0">
-        <v>0.059247376894118922</v>
+        <v>0.059073967429011415</v>
       </c>
       <c r="B112" s="0">
-        <v>0.12687120897450613</v>
+        <v>0.12709029803750371</v>
       </c>
       <c r="C112" s="0">
-        <v>0.19034604550285045</v>
+        <v>0.18310379253271411</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0">
-        <v>0.06680867304619395</v>
+        <v>0.066757820955275798</v>
       </c>
       <c r="B113" s="0">
-        <v>0.13878435155768001</v>
+        <v>0.13877086220945534</v>
       </c>
       <c r="C113" s="0">
-        <v>0.19901963411988949</v>
+        <v>0.19700369681570157</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0">
-        <v>0.074944908654705808</v>
+        <v>0.074289015138761974</v>
       </c>
       <c r="B114" s="0">
-        <v>0.15015263816671459</v>
+        <v>0.14894905207461454</v>
       </c>
       <c r="C114" s="0">
-        <v>0.20143516316476529</v>
+        <v>0.20307292734229002</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0">
-        <v>0.081737507233414497</v>
+        <v>0.081272536517915508</v>
       </c>
       <c r="B115" s="0">
-        <v>0.15881606893374617</v>
+        <v>0.15821243627150741</v>
       </c>
       <c r="C115" s="0">
-        <v>0.20671111796803063</v>
+        <v>0.20273173039993078</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0">
-        <v>0.085958095275363397</v>
+        <v>0.085632453280453394</v>
       </c>
       <c r="B116" s="0">
-        <v>0.16442609325120625</v>
+        <v>0.16449239712923158</v>
       </c>
       <c r="C116" s="0">
-        <v>0.20254327300787778</v>
+        <v>0.19378164643007426</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0">
-        <v>0.089539403727808789</v>
+        <v>0.08964401536385963</v>
       </c>
       <c r="B117" s="0">
-        <v>0.1700008942763406</v>
+        <v>0.1701550724886326</v>
       </c>
       <c r="C117" s="0">
-        <v>0.19635448581840925</v>
+        <v>0.19483166744103547</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0">
-        <v>0.092565820557188566</v>
+        <v>0.09212062768668014</v>
       </c>
       <c r="B118" s="0">
-        <v>0.1755425974042536</v>
+        <v>0.17447981271708449</v>
       </c>
       <c r="C118" s="0">
-        <v>0.20703613480664618</v>
+        <v>0.21046684905449126</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0">
-        <v>0.093398507987144136</v>
+        <v>0.093200181226037751</v>
       </c>
       <c r="B119" s="0">
-        <v>0.17808756616194982</v>
+        <v>0.17741087788025994</v>
       </c>
       <c r="C119" s="0">
-        <v>0.19877940058081964</v>
+        <v>0.19558516897054315</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0">
-        <v>0.089854349668574807</v>
+        <v>0.089534046400041006</v>
       </c>
       <c r="B120" s="0">
-        <v>0.17436547389655835</v>
+        <v>0.17368066687297512</v>
       </c>
       <c r="C120" s="0">
-        <v>0.17317980049145332</v>
+        <v>0.16355785799441239</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0">
-        <v>0.076086162538721622</v>
+        <v>0.075785203703043674</v>
       </c>
       <c r="B121" s="0">
-        <v>0.15983947229893816</v>
+        <v>0.15900832222931094</v>
       </c>
       <c r="C121" s="0">
-        <v>0.14401594933787262</v>
+        <v>0.14371681373052614</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0">
-        <v>0.050510770919341565</v>
+        <v>0.050090764484086364</v>
       </c>
       <c r="B122" s="0">
-        <v>0.13501985551125456</v>
+        <v>0.13516016392736305</v>
       </c>
       <c r="C122" s="0">
-        <v>0.10534313758244275</v>
+        <v>0.10937402293995473</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0">
-        <v>0.024280324590185958</v>
+        <v>0.024167631998207945</v>
       </c>
       <c r="B123" s="0">
-        <v>0.11424353315887729</v>
+        <v>0.11430881946380982</v>
       </c>
       <c r="C123" s="0">
-        <v>0.051895919860802761</v>
+        <v>0.049219336919913342</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0">
-        <v>0.0039160201874155649</v>
+        <v>0.0034572709606371273</v>
       </c>
       <c r="B124" s="0">
-        <v>0.097312627553620551</v>
+        <v>0.097157292063336315</v>
       </c>
       <c r="C124" s="0">
-        <v>0.02716614113073762</v>
+        <v>0.017347873866299966</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0">
-        <v>-0.0079459628805124104</v>
+        <v>-0.0078772221079886524</v>
       </c>
       <c r="B125" s="0">
-        <v>0.082122169211607116</v>
+        <v>0.082279819051063213</v>
       </c>
       <c r="C125" s="0">
-        <v>0.025164941736583693</v>
+        <v>0.02589668722091518</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0">
-        <v>-0.014928908379259051</v>
+        <v>-0.015063374967427004</v>
       </c>
       <c r="B126" s="0">
-        <v>0.062830403239599944</v>
+        <v>0.062280334183346928</v>
       </c>
       <c r="C126" s="0">
-        <v>0.021933974047411358</v>
+        <v>0.027760530648121406</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0">
-        <v>-0.019223115184684642</v>
+        <v>-0.019384920191044763</v>
       </c>
       <c r="B127" s="0">
-        <v>0.03830345064693555</v>
+        <v>0.03770266264662378</v>
       </c>
       <c r="C127" s="0">
-        <v>0.011542828209232043</v>
+        <v>0.0065386280645948897</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0">
-        <v>-0.020161818993591481</v>
+        <v>-0.020515037092398627</v>
       </c>
       <c r="B128" s="0">
-        <v>0.015734542082799653</v>
+        <v>0.014749507999352783</v>
       </c>
       <c r="C128" s="0">
-        <v>0.00086852637066400784</v>
+        <v>-0.0085936251204376569</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0">
-        <v>-0.019680848781699938</v>
+        <v>-0.020242870265400989</v>
       </c>
       <c r="B129" s="0">
-        <v>-0.0015479180066989146</v>
+        <v>-0.002752506578321566</v>
       </c>
       <c r="C129" s="0">
-        <v>-0.014743579611776155</v>
+        <v>-0.013218865785670612</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0">
-        <v>-0.016514091045699317</v>
+        <v>-0.016426018278004471</v>
       </c>
       <c r="B130" s="0">
-        <v>-0.011370200820048724</v>
+        <v>-0.010344545465408618</v>
       </c>
       <c r="C130" s="0">
-        <v>-0.035104496559091883</v>
+        <v>-0.030363327122324098</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0">
-        <v>-0.013662571545672561</v>
+        <v>-0.013756931828847496</v>
       </c>
       <c r="B131" s="0">
-        <v>-0.014617068483199037</v>
+        <v>-0.0145671622370852</v>
       </c>
       <c r="C131" s="0">
-        <v>-0.052193915670835415</v>
+        <v>-0.056762190199243556</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0">
-        <v>-0.015503971806137003</v>
+        <v>-0.015864741150393536</v>
       </c>
       <c r="B132" s="0">
-        <v>-0.019788041369572028</v>
+        <v>-0.020254644964936733</v>
       </c>
       <c r="C132" s="0">
-        <v>-0.084479431832359952</v>
+        <v>-0.091465552915217282</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0">
-        <v>-0.019030695120327044</v>
+        <v>-0.018656914847430185</v>
       </c>
       <c r="B133" s="0">
-        <v>-0.025374545321338395</v>
+        <v>-0.024930275641518236</v>
       </c>
       <c r="C133" s="0">
-        <v>-0.1166995385642902</v>
+        <v>-0.11173001338134557</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0">
-        <v>-0.025458410337405171</v>
+        <v>-0.026025509896182738</v>
       </c>
       <c r="B134" s="0">
-        <v>-0.033382672187711293</v>
+        <v>-0.033728613012081368</v>
       </c>
       <c r="C134" s="0">
-        <v>-0.11381113435389281</v>
+        <v>-0.11344927197288589</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0">
-        <v>-0.030123391736487065</v>
+        <v>-0.030316766631734965</v>
       </c>
       <c r="B135" s="0">
-        <v>-0.036833551702112985</v>
+        <v>-0.037393945161888639</v>
       </c>
       <c r="C135" s="0">
-        <v>-0.13558137523861627</v>
+        <v>-0.14029513064132104</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0">
-        <v>-0.034847982677586133</v>
+        <v>-0.035151410980632555</v>
       </c>
       <c r="B136" s="0">
-        <v>-0.040373442230933129</v>
+        <v>-0.041016962724579449</v>
       </c>
       <c r="C136" s="0">
-        <v>-0.15296503826038121</v>
+        <v>-0.15756827765029119</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0">
-        <v>-0.039348796961963847</v>
+        <v>-0.039314550801801837</v>
       </c>
       <c r="B137" s="0">
-        <v>-0.041686409156189951</v>
+        <v>-0.04145881297166501</v>
       </c>
       <c r="C137" s="0">
-        <v>-0.15266325089768834</v>
+        <v>-0.14928614846932478</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0">
-        <v>-0.039281102953947378</v>
+        <v>-0.039322330966016353</v>
       </c>
       <c r="B138" s="0">
-        <v>-0.03571244427043975</v>
+        <v>-0.035439567968243033</v>
       </c>
       <c r="C138" s="0">
-        <v>-0.1611505469647222</v>
+        <v>-0.16023405113146832</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0">
-        <v>-0.037731994346178979</v>
+        <v>-0.03776215320515907</v>
       </c>
       <c r="B139" s="0">
-        <v>-0.033054915146493995</v>
+        <v>-0.033893258036347851</v>
       </c>
       <c r="C139" s="0">
-        <v>-0.16371200943399528</v>
+        <v>-0.16894717894918687</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0">
-        <v>-0.034075826328519521</v>
+        <v>-0.034173439755035957</v>
       </c>
       <c r="B140" s="0">
-        <v>-0.032240848778730201</v>
+        <v>-0.033477612077465212</v>
       </c>
       <c r="C140" s="0">
-        <v>-0.14708168977485692</v>
+        <v>-0.14959702019348925</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0">
-        <v>-0.029519113995856966</v>
+        <v>-0.03007182035607639</v>
       </c>
       <c r="B141" s="0">
-        <v>-0.0346199865428495</v>
+        <v>-0.035500479474806002</v>
       </c>
       <c r="C141" s="0">
-        <v>-0.13968311749907372</v>
+        <v>-0.13564461842215123</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0">
-        <v>-0.023926962270673632</v>
+        <v>-0.024055140827796563</v>
       </c>
       <c r="B142" s="0">
-        <v>-0.040514854360507481</v>
+        <v>-0.039124829385826454</v>
       </c>
       <c r="C142" s="0">
-        <v>-0.12537765882715715</v>
+        <v>-0.12782825697593786</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0">
-        <v>-0.025067001853253425</v>
+        <v>-0.024979235977794171</v>
       </c>
       <c r="B143" s="0">
-        <v>-0.054543618745726039</v>
+        <v>-0.05471817807177403</v>
       </c>
       <c r="C143" s="0">
-        <v>-0.10980181204501012</v>
+        <v>-0.11327492511245776</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0">
-        <v>-0.025391832886424492</v>
+        <v>-0.025456035676783562</v>
       </c>
       <c r="B144" s="0">
-        <v>-0.062956113084982682</v>
+        <v>-0.063475800960446416</v>
       </c>
       <c r="C144" s="0">
-        <v>-0.088106968276277772</v>
+        <v>-0.088077465742811195</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0">
-        <v>-0.023092194996460383</v>
+        <v>-0.023078810240029793</v>
       </c>
       <c r="B145" s="0">
-        <v>-0.067937322151093119</v>
+        <v>-0.067399136877264232</v>
       </c>
       <c r="C145" s="0">
-        <v>-0.079085331610763546</v>
+        <v>-0.076318983521419331</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0">
-        <v>-0.01813669584070917</v>
+        <v>-0.018308767698785033</v>
       </c>
       <c r="B146" s="0">
-        <v>-0.068649428542547158</v>
+        <v>-0.068451082793183959</v>
       </c>
       <c r="C146" s="0">
-        <v>-0.086371874097632514</v>
+        <v>-0.087319089868321056</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0">
-        <v>-0.009606784448479417</v>
+        <v>-0.0099303430732821142</v>
       </c>
       <c r="B147" s="0">
-        <v>-0.065730965757071325</v>
+        <v>-0.066739374467301049</v>
       </c>
       <c r="C147" s="0">
-        <v>-0.067640384753597044</v>
+        <v>-0.071872005651340415</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0">
-        <v>-0.0032493120174483942</v>
+        <v>-0.0031866721849335942</v>
       </c>
       <c r="B148" s="0">
-        <v>-0.064909604285719541</v>
+        <v>-0.065190694736589366</v>
       </c>
       <c r="C148" s="0">
-        <v>-0.064726238157149535</v>
+        <v>-0.064217900415714846</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0">
-        <v>-0.0022120360284541875</v>
+        <v>-0.0019986508324478618</v>
       </c>
       <c r="B149" s="0">
-        <v>-0.064283909765552802</v>
+        <v>-0.063552973470629437</v>
       </c>
       <c r="C149" s="0">
-        <v>-0.067316862051508081</v>
+        <v>-0.06501592734293081</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0">
-        <v>-0.0077661933127726387</v>
+        <v>-0.008198290434034302</v>
       </c>
       <c r="B150" s="0">
-        <v>-0.06909666182319979</v>
+        <v>-0.069422318202596228</v>
       </c>
       <c r="C150" s="0">
-        <v>-0.074082785031233681</v>
+        <v>-0.076787528520963419</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0">
-        <v>-0.013157531908564361</v>
+        <v>-0.013220769840684233</v>
       </c>
       <c r="B151" s="0">
-        <v>-0.068065950137655873</v>
+        <v>-0.0690169189648253</v>
       </c>
       <c r="C151" s="0">
-        <v>-0.073562056066855827</v>
+        <v>-0.075375249964044044</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0">
-        <v>-0.018690236665389791</v>
+        <v>-0.018260638391326207</v>
       </c>
       <c r="B152" s="0">
-        <v>-0.062444090377747438</v>
+        <v>-0.062835303691945926</v>
       </c>
       <c r="C152" s="0">
-        <v>-0.073631066655687236</v>
+        <v>-0.07268920093004809</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0">
-        <v>-0.023084134407999678</v>
+        <v>-0.023330235106052723</v>
       </c>
       <c r="B153" s="0">
-        <v>-0.053058848714227405</v>
+        <v>-0.053453821350827831</v>
       </c>
       <c r="C153" s="0">
-        <v>-0.068543558853611922</v>
+        <v>-0.06821173502592083</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0">
-        <v>-0.013139245891107763</v>
+        <v>-0.013784350947457599</v>
       </c>
       <c r="B154" s="0">
-        <v>-0.023834691939249468</v>
+        <v>-0.023574931734311168</v>
       </c>
       <c r="C154" s="0">
-        <v>-0.047584587615577732</v>
+        <v>-0.049150311722441359</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0">
-        <v>-0.0064022549341020011</v>
+        <v>-0.0064186329531310303</v>
       </c>
       <c r="B155" s="0">
-        <v>-0.016390321935661728</v>
+        <v>-0.016469972123834893</v>
       </c>
       <c r="C155" s="0">
-        <v>-0.047409477775819837</v>
+        <v>-0.047271086952474776</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0">
-        <v>-0.0044541280464068357</v>
+        <v>-0.0038557019215278558</v>
       </c>
       <c r="B156" s="0">
-        <v>-0.017648689010001151</v>
+        <v>-0.016933986763774139</v>
       </c>
       <c r="C156" s="0">
-        <v>-0.036747938451036147</v>
+        <v>-0.036302971388545005</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0">
-        <v>-0.0051965551596095168</v>
+        <v>-0.0051161966709620263</v>
       </c>
       <c r="B157" s="0">
-        <v>-0.018118091266019518</v>
+        <v>-0.017773564174906914</v>
       </c>
       <c r="C157" s="0">
-        <v>-0.028632175234889638</v>
+        <v>-0.029939974374793153</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0">
-        <v>-0.0042394753185734813</v>
+        <v>-0.0049299029320713479</v>
       </c>
       <c r="B158" s="0">
-        <v>-0.017725999439719781</v>
+        <v>-0.018722258495835181</v>
       </c>
       <c r="C158" s="0">
-        <v>-0.018861102441309618</v>
+        <v>-0.017326067011148319</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0">
-        <v>-0.0071370350299647858</v>
+        <v>-0.0073780968594456481</v>
       </c>
       <c r="B159" s="0">
-        <v>-0.019944500856405478</v>
+        <v>-0.020265077724529835</v>
       </c>
       <c r="C159" s="0">
-        <v>-0.0066248225570649313</v>
+        <v>-0.0075646117829874845</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0">
-        <v>-0.0093398921486398459</v>
+        <v>-0.0085903311576019537</v>
       </c>
       <c r="B160" s="0">
-        <v>-0.016864262604774329</v>
+        <v>-0.016033309741677864</v>
       </c>
       <c r="C160" s="0">
-        <v>-0.0062287064942282942</v>
+        <v>-0.0066302680034788768</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0">
-        <v>-0.013903575636752919</v>
+        <v>-0.013873680862375039</v>
       </c>
       <c r="B161" s="0">
-        <v>-0.019374818479391643</v>
+        <v>-0.019399207108732931</v>
       </c>
       <c r="C161" s="0">
-        <v>-0.010928078107898349</v>
+        <v>-0.013053569156913698</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0">
-        <v>-0.018137238590697768</v>
+        <v>-0.018924651557471087</v>
       </c>
       <c r="B162" s="0">
-        <v>-0.02338970975628693</v>
+        <v>-0.024427243608333368</v>
       </c>
       <c r="C162" s="0">
-        <v>-0.01874706114036653</v>
+        <v>-0.016395893312454769</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0">
-        <v>-0.01598922364482314</v>
+        <v>-0.016076082848772894</v>
       </c>
       <c r="B163" s="0">
-        <v>-0.022932795985883683</v>
+        <v>-0.022859237544412988</v>
       </c>
       <c r="C163" s="0">
-        <v>-0.020439489663105641</v>
+        <v>-0.020331780140907037</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0">
-        <v>-0.0094917370920094002</v>
+        <v>-0.00865568288507855</v>
       </c>
       <c r="B164" s="0">
-        <v>-0.026382886115385029</v>
+        <v>-0.025567888421144252</v>
       </c>
       <c r="C164" s="0">
-        <v>-0.02606801301463689</v>
+        <v>-0.02657922251489532</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0">
-        <v>-0.0068233935292632622</v>
+        <v>-0.0065649627979261146</v>
       </c>
       <c r="B165" s="0">
-        <v>-0.041775482507339479</v>
+        <v>-0.041781071157035651</v>
       </c>
       <c r="C165" s="0">
-        <v>-0.034317969386064809</v>
+        <v>-0.033824151337588149</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0">
-        <v>-0.018606215705463242</v>
+        <v>-0.019957222062357505</v>
       </c>
       <c r="B166" s="0">
-        <v>-0.068331620769752868</v>
+        <v>-0.069681916692537704</v>
       </c>
       <c r="C166" s="0">
-        <v>-0.041918515718369589</v>
+        <v>-0.042203982025187187</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="0">
-        <v>-0.037047175085481832</v>
-      </c>
-      <c r="B167" s="0">
-        <v>-0.082542981922212266</v>
-      </c>
-      <c r="C167" s="0">
-        <v>-0.055767949896967609</v>
-      </c>
+      <c r="A167" s="0"/>
+      <c r="B167" s="0"/>
+      <c r="C167" s="0"/>
     </row>
     <row r="168">
       <c r="A168" s="0"/>
